--- a/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
   <si>
     <t>DB</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9399300</v>
+        <v>9160300</v>
       </c>
       <c r="E8" s="3">
+        <v>9401600</v>
+      </c>
+      <c r="F8" s="3">
         <v>7831400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8947600</v>
       </c>
-      <c r="G8" s="3">
-        <v>9121600</v>
-      </c>
       <c r="H8" s="3">
+        <v>8665900</v>
+      </c>
+      <c r="I8" s="3">
         <v>8705100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8505000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7812800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8056400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7483000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6822200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7288300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7651700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7941100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9102300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6928400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5707100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4801100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4626900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4467000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4179100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4479600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3846000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4143300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4898200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5964000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6438300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7751700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8073600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7778900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7110400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6720900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7042600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6582500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5961100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6681500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7024800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7056900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7657900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>7464300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>9399300</v>
+        <v>9160300</v>
       </c>
       <c r="E10" s="3">
+        <v>9401600</v>
+      </c>
+      <c r="F10" s="3">
         <v>7831400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8947600</v>
       </c>
-      <c r="G10" s="3">
-        <v>9121600</v>
-      </c>
       <c r="H10" s="3">
+        <v>8665900</v>
+      </c>
+      <c r="I10" s="3">
         <v>8705100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8505000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7812800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8056400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7483000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6822200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7288300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7651700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7941100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,50 +1467,53 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>218400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>-5400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2318000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-75800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-49300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>696400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>146300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>916800</v>
+      </c>
+      <c r="E15" s="3">
         <v>272700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>277700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>463500</v>
       </c>
-      <c r="G15" s="3">
-        <v>786300</v>
-      </c>
       <c r="H15" s="3">
+        <v>840300</v>
+      </c>
+      <c r="I15" s="3">
         <v>256700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>245900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>338500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>569500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>327400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>335500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>490600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>645700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>503600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6100800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5893000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6010300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6076500</v>
       </c>
-      <c r="G17" s="3">
-        <v>5818000</v>
-      </c>
       <c r="H17" s="3">
+        <v>5822700</v>
+      </c>
+      <c r="I17" s="3">
         <v>5644200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4121500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5365800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7232400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5721200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5353200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5465700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5971600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5928900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5351900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3346900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2292600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1996400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1733500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1605700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1446300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1589100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1539000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1706300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2354200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2969500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2912700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3733800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3942100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3931900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3275500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3102400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3343400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2729800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3263900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3657700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3624700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4049600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3710400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3506300</v>
+        <v>3059500</v>
       </c>
       <c r="E18" s="3">
+        <v>3508600</v>
+      </c>
+      <c r="F18" s="3">
         <v>1821100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2871100</v>
       </c>
-      <c r="G18" s="3">
-        <v>3303600</v>
-      </c>
       <c r="H18" s="3">
+        <v>2843200</v>
+      </c>
+      <c r="I18" s="3">
         <v>3061000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4383500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2447000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>824000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1761800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1469000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1822600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1680100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2012200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3750300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3581400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3414500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2804700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2893500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2861300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2732800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2890500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2307000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2437000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2544000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2994500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3525600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4018000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4131500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3847000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3835000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3618500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3699200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3143600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3231300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3417600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3367100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3432200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3608300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3753800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,131 +2101,134 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2893100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1836100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1731200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1005800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2804600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2264700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1500200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1209300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2132400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1936700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2371600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5035000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4859500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5244400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3496500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4213500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3058100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2918500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2669200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-4807700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2370800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2444800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2401600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-6444200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-3027300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3779000</v>
+        <v>3976400</v>
       </c>
       <c r="E21" s="3">
+        <v>3781300</v>
+      </c>
+      <c r="F21" s="3">
         <v>2098700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3334500</v>
       </c>
-      <c r="G21" s="3">
-        <v>4089800</v>
-      </c>
       <c r="H21" s="3">
+        <v>3683500</v>
+      </c>
+      <c r="I21" s="3">
         <v>3317700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4629400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2785500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1393400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2089200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1804500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2313200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2325900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2515800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2238,38 +2274,41 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>326500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1252700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>822400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-843700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1413700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1466400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1845200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-225400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1150300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3505100</v>
+        <v>3060700</v>
       </c>
       <c r="E23" s="3">
+        <v>3507400</v>
+      </c>
+      <c r="F23" s="3">
         <v>1602700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2868700</v>
       </c>
-      <c r="G23" s="3">
-        <v>3303600</v>
-      </c>
       <c r="H23" s="3">
+        <v>2843200</v>
+      </c>
+      <c r="I23" s="3">
         <v>3066400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2065400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2522900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>873200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1760700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>772600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1822600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1533800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2012200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>857300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1745300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1683300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1798900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>88900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>596600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1232600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1681200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>174500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>500300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>172400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>224700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1509500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-841600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1112900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>350500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-378500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>560400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>780700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>474300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1576400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1046800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>922300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1030600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2835900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>726600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>999700</v>
+        <v>884300</v>
       </c>
       <c r="E24" s="3">
+        <v>1000800</v>
+      </c>
+      <c r="F24" s="3">
         <v>136200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>734500</v>
       </c>
-      <c r="G24" s="3">
-        <v>938300</v>
-      </c>
       <c r="H24" s="3">
+        <v>808000</v>
+      </c>
+      <c r="I24" s="3">
         <v>891700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>707100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>665800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>507900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>506000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-808000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>552500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>508700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>575800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1332400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>402000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>365600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>467600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-253700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>242300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>357600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>584000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>179600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>105800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>153800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>223000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>177600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2592800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>108900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>105300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>306800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>340400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>342600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1143300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>318600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>400600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>355700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-616300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>399100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2505500</v>
+        <v>2176400</v>
       </c>
       <c r="E26" s="3">
+        <v>2506600</v>
+      </c>
+      <c r="F26" s="3">
         <v>1466500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2134200</v>
       </c>
-      <c r="G26" s="3">
-        <v>2365200</v>
-      </c>
       <c r="H26" s="3">
+        <v>2035200</v>
+      </c>
+      <c r="I26" s="3">
         <v>2174700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1358300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1857000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>365400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1254700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1580600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1270100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1025100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1436300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2189700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1343300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1317700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1331300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>342600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>354300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>875000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1097100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>188500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>320700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>66500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>70900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1732400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1019200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3705700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>241600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-483800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>253600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>440300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>131800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2719700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>728200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>521700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>674900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-2219700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>327500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2442100</v>
+        <v>1259000</v>
       </c>
       <c r="E27" s="3">
+        <v>2387900</v>
+      </c>
+      <c r="F27" s="3">
         <v>488400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2080300</v>
       </c>
-      <c r="G27" s="3">
-        <v>2311200</v>
-      </c>
       <c r="H27" s="3">
+        <v>1126200</v>
+      </c>
+      <c r="I27" s="3">
         <v>2127100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>729900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1821300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>316100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1224500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1546400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1244700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>438900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1409200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2020300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1205000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1138200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1150100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>225500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>208900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>732100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>960700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>83800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>188900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-46900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>117200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-502700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>233700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>310700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>47200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2720800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>725900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>178400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>670200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1612300</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>2893100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1836100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1731200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1005800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2804600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2264700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1500200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1209300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2132400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1936700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2371600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2769800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5035000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4859500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5244400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3496500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4213500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3058100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2918500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2669200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>4807700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2370800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2444800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2401600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>6444200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>3027300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2442100</v>
+        <v>2113600</v>
       </c>
       <c r="E33" s="3">
+        <v>2443200</v>
+      </c>
+      <c r="F33" s="3">
         <v>1381900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2080300</v>
       </c>
-      <c r="G33" s="3">
-        <v>2311200</v>
-      </c>
       <c r="H33" s="3">
+        <v>1981200</v>
+      </c>
+      <c r="I33" s="3">
         <v>2127100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1324200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1821300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>316100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1224500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1546400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1244700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>982500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1409200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2020300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1205000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1138200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1150100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>225500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>208900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>732100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>960700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>83800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>188900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-46900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>117200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-502700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>233700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>310700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>47200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>725900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>178400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>670200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2442100</v>
+        <v>2113600</v>
       </c>
       <c r="E35" s="3">
+        <v>2443200</v>
+      </c>
+      <c r="F35" s="3">
         <v>1381900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2080300</v>
       </c>
-      <c r="G35" s="3">
-        <v>2311200</v>
-      </c>
       <c r="H35" s="3">
+        <v>1981200</v>
+      </c>
+      <c r="I35" s="3">
         <v>2127100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1324200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1821300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>316100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1224500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1546400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1244700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>982500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1409200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2020300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1205000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1138200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1150100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>225500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>208900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>732100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>960700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>83800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>188900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-46900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>117200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-502700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>233700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>310700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>47200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>725900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>178400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>670200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>147319800</v>
+      </c>
+      <c r="E41" s="3">
         <v>160870500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>162354100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>163843700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>144204300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>163802400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>135279000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>157295300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>144281600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>159928800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>181019100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>179591400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>163784900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>174681700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>198145200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>196741400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>192669900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>181637700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>208170000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>212033000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>209767500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>190419900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>165775900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>183905500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>181344200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>132965600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>160626300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>205606000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>189379200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>224065000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>223249900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>222838000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>228478400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>248938600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>253182700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>229323500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>255268400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>210653100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>212886900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>127064900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>579604700</v>
+      </c>
+      <c r="E42" s="3">
         <v>557335400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>661322100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>503991600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>549899000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>465543700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>607604300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>475900100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>448251400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>417080600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>531073300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>438541500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>436538200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>398974400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>557349900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>656241000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>579888700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>550086300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>549645200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>534165000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>514620700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>534342900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>545724400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>583172100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>643250700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>720305000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>647419900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>844378300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>764585900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>754124000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>709886700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>662362500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>684587600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>720950100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>857440500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>785621900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>805357700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>892835100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>929369900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1053154100</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1792500</v>
+      </c>
+      <c r="E43" s="3">
         <v>13777200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>56650200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11506500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2042300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9971900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45537800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10383700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1676800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10500600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46065000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8226100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1694300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8101900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,52 +4774,55 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>74393600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>23927900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>40413400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>728728400</v>
+      </c>
+      <c r="E46" s="3">
         <v>731983200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>954720000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>679341800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>696145600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>639318000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>812349100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>643579100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>594209800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>587510000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>798570800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>626368500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>602031700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>581757900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>219255100</v>
+      </c>
+      <c r="E47" s="3">
         <v>200739100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>103432000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>180516300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>188525000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>167032000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66909600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187103500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>156162000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>149951500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>71676800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>130016900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>134200900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>141440700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1244900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1344400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1289400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1159900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1182800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1164100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1174400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1123600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>898700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>955900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1035300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>999300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1084500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1118400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1081100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1101700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1039800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>940400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>934400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>986000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>971600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1026600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1063600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1150300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1205500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1089300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6697100</v>
+      </c>
+      <c r="E48" s="3">
         <v>6841900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6955500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7045600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7092200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6665600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6411600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6854800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6663500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6747200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6836500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6490300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6561100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6628600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6759700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6435600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6087900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6035900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6001600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5725900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5689900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5773500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5534600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5979300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5253800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5238500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5755300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6297700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6274900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6506100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2775600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2788900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2693400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2987900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3110200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3081000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3324200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3291400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3165800</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8960400</v>
+      </c>
+      <c r="E49" s="3">
         <v>8930000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8877500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8800900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8705800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8243600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8022600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8331500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8087400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8049400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8098800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7761400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7795900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7701000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7855100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7996100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7785400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7488700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7397900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7242200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7243100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7249400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6707500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7004800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7527300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7633100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8205700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9371200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9067700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10984700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10812900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10030400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9862200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9608600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9917300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9843200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>9911700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10610100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>10543200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>11221600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>213779300</v>
+      </c>
+      <c r="E52" s="3">
         <v>200916600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39216900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>197450400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>185168500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>187452400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31260000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>159509300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>163554100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>162672300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32293600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>151866000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>140250000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>150403100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8054500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6742500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6896400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6949400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6740900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6332200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6231600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6278200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6042200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6341600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6508400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6412400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6988100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7394000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6532500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8867400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11721400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>15922900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10640700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10177400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7678900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9295700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9479700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>10552600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>10833100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>13272300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1738254300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1709935400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1690587100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1632343100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1646056400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1531395400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1440141800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1539250500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1447986700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1435737400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1450570400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1437629100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1419533800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1419792500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1480626400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1618961000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1508824700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1457226600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1435340800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1428031900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1396966300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1393519300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1321813300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1440388300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1535233300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1626768300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1514917600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1838614400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1689423300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1719153500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1594711300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1528468100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1560214100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1622553000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1654634600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1707056200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1760103900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1836726200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1866998800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1982507600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,80 +6116,81 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>797654500</v>
+      </c>
+      <c r="E57" s="3">
         <v>791719100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>815521900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>777843500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>768781000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>718679200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>691272400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>724824900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>686713800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>684731900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>687559400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>647020500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>647623400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>643130200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3130100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>1761700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1735500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
@@ -6079,83 +6209,86 @@
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>2940700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2523100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2478200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2882300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2943000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2793800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3097800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3379400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3183400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2699800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>325887100</v>
+      </c>
+      <c r="E58" s="3">
         <v>320555700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>420463800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>268362100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>298285400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>252522700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>396425100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>267756000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>251066100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>241637700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>393319300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>297073500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>273882100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>257766200</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>58905500</v>
+      </c>
+      <c r="E59" s="3">
         <v>56113200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>181929100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>53659500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56584900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>55089700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>116109300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56543600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57139200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>52004500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>140061900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54442200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>63190000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>66303800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>429700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>595500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>750800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>768200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>650500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>855100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>921500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>815700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>572500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>714100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>836700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>711300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>760000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>851400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2138700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1063400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1116700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>985800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1012400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1213300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1123100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1205000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1212900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1304100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1560000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1480200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1182447200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1168388100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1423679700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1099865100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1123651200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1026291600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1209100300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1049124500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>994919100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>978374200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1226229700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>998536200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>984695400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>967200100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>296443500</v>
+      </c>
+      <c r="E61" s="3">
         <v>278827400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144194000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>273304000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>261520800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>241588800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>122314900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>243473100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>218753900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>208782000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>113130300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>216167400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>222489100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>227269700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>206743500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>220125600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>222566500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>210513900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>220593800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>224408700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>214884000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>210056400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>196553600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>216575500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>227441600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>217812200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>220428000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>255682400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>238475100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>267994300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>190280100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>179290500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>183304500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>188645200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>192592900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>192494200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>199071300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>218534100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>217392000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>206663300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166746300</v>
+      </c>
+      <c r="E62" s="3">
         <v>170119900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25403300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>165918100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>165780400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>174706000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23377200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>160714900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>153011900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>166052400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27908700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>143983900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>132271800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>144923900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3662800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3503600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3722400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4141400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3679400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3266200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3242800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3485100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12807600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3260000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3497500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3710200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3697200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3912600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3751500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4158000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5281600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>9456700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7174300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9655800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5071400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6957500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7417500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9514900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>14273500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>12366100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1646401200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1618102200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1593974400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1539795800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1551635900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1443233900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1355386700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1453963900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1367338500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1353861300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1367872200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1359420000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1340151700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1340068400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1402499600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1544340800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1435795800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1384556600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1363430300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1358786100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1329638300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1328013200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1261361900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1377499800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1468503400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1559431800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1444263600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1761414300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1614819600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1638303600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1515257000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1453978600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1486283500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1549409800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1578508700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1628130900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1680518900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1760945100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1791284500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1904516100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>33421700</v>
+      </c>
+      <c r="E72" s="3">
         <v>34723900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>35546600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31195600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>32301800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27329200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26785400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25510800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22809400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24599200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23561400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21350600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20796900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20953900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19715300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17009100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15720900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15034800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13667200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13118800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12484400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11771300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>9988000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>9959700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10335300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>10680000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11258500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14121700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14850900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19841400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19771000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19008600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18649500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18846100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19583200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>22200800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>21747500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>22878700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>22287100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>24485700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>90053700</v>
+      </c>
+      <c r="E76" s="3">
         <v>89949300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>94778700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90787300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>92709300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>86467800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>83092500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83553400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>78952100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>79919100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>80749400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>76331500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>77501100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>77770500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>78126800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>74620200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>73028900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>72670000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>71910500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>69245700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>67327900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>65506100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60451400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>62888400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>66729900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>67336400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>70654000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>77200100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>74603800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>80850000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>79454200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>74489400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>73930500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>73143300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>76125900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>78925300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>79585000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>75781200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>75714300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>77991500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2442100</v>
+        <v>2113600</v>
       </c>
       <c r="E81" s="3">
+        <v>2443200</v>
+      </c>
+      <c r="F81" s="3">
         <v>1381900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2080300</v>
       </c>
-      <c r="G81" s="3">
-        <v>2311200</v>
-      </c>
       <c r="H81" s="3">
+        <v>1981200</v>
+      </c>
+      <c r="I81" s="3">
         <v>2127100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1324200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1821300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>316100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1224500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1546400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1244700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>982500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1409200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2020300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1205000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1138200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1150100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>225500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>208900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>732100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>960700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>83800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>188900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-84000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-46900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1870200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1153900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3849200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>117200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-502700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>233700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>310700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>47200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-4333100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>725900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>178400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>670200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-2217300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>300500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,23 +9006,23 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
@@ -8832,8 +9030,8 @@
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -8853,41 +9051,44 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>705000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>692300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>936600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>348100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>732700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>366900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>544200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>814600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>2610600</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>423700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,8 +9709,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9540,23 +9756,23 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
@@ -9564,8 +9780,8 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -9585,41 +9801,44 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-14742500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-7702300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-25258400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-12785100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>22428600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-24901400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>49922900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-3185700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>72411200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-24445800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,32 +9926,32 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-249000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-331000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-181000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -9751,41 +9971,44 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-153800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-109800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-105400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-71800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-170500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-139100</v>
-      </c>
-      <c r="AN91" s="3">
-        <v>-340400</v>
       </c>
       <c r="AO91" s="3">
         <v>-340400</v>
       </c>
       <c r="AP91" s="3">
+        <v>-340400</v>
+      </c>
+      <c r="AQ91" s="3">
         <v>-208900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,8 +10254,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10072,23 +10301,23 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
@@ -10096,8 +10325,8 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -10117,41 +10346,44 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-923800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1684700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5880900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5028800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1605600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1331800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-448800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>252400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>11937600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>5980600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10305,19 +10538,22 @@
         <v>0</v>
       </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-439800</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,8 +10924,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10726,23 +10971,23 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
@@ -10750,8 +10995,8 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -10771,41 +11016,44 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-132500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-332300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2414500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-793900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>911100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-371400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>7601500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-138500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-59900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-217200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,23 +11096,23 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
@@ -10872,8 +11120,8 @@
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -10893,41 +11141,44 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>1113100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>875000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1412000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1481200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1384500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2435800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1992700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-693700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>430800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>110300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10970,23 +11221,23 @@
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
@@ -10994,8 +11245,8 @@
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -11015,37 +11266,40 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-14811100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8844200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-20380000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10031300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>23560700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-26376900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>55083000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-3765600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>84719700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-18572000</v>
       </c>
     </row>
